--- a/tables/resultados_propostas_lira.xlsx
+++ b/tables/resultados_propostas_lira.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -469,25 +469,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10% de IR Mínimo</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.6165899422660595</v>
+      </c>
+      <c r="C5">
+        <v>0.1406696751015247</v>
+      </c>
+      <c r="D5">
+        <v>0.1406696751015247</v>
+      </c>
+      <c r="E5">
+        <v>0.2421434918316321</v>
+      </c>
+      <c r="F5">
+        <v>360.6340583975178</v>
+      </c>
+      <c r="G5">
+        <v>25.93848051235375</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Lucros e Dividendos</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>0.6151503109828721</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>0.1412687326280157</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>0.5449906159338507</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <v>0.2407998888084555</v>
       </c>
-      <c r="F5">
+      <c r="F6">
         <v>335.7324994600784</v>
       </c>
-      <c r="G5">
+      <c r="G6">
         <v>1.036921574914288</v>
       </c>
     </row>
